--- a/Code and data/Final data/Coverage_Report.xlsx
+++ b/Code and data/Final data/Coverage_Report.xlsx
@@ -449,7 +449,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GHG_Emissions_Scope1</t>
+          <t>Scope1_Emissions</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/Code and data/Final data/Coverage_Report.xlsx
+++ b/Code and data/Final data/Coverage_Report.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rd_e_berdindr2 + demo_r_d2jan</t>
+          <t>rd_e_gerdreg (sectperf=BES, PC_GDP)</t>
         </is>
       </c>
       <c r="C13">
